--- a/server/data/imports/uber/uber.xlsx
+++ b/server/data/imports/uber/uber.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mon Drive\Donnuts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nprin\Freda cockpit V31\server\data\imports\uber\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C482DA-D024-4123-80B4-C932CACAC2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1144835C-2244-485B-AB67-CE28E1C6284A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A100726-893B-4AF6-887A-6E8D99DEE1FA}"/>
   </bookViews>
@@ -468,7 +468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0258365A-ED26-4117-A724-7F37F5D696E5}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:N148"/>
+  <dimension ref="A1:N155"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -2550,6 +2550,104 @@
         <v>1141</v>
       </c>
     </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B149">
+        <v>192</v>
+      </c>
+      <c r="C149">
+        <v>351</v>
+      </c>
+      <c r="D149">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B150">
+        <v>169</v>
+      </c>
+      <c r="C150">
+        <v>310</v>
+      </c>
+      <c r="D150">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>469</v>
+      </c>
+      <c r="D151">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B152">
+        <v>151</v>
+      </c>
+      <c r="C152">
+        <v>565</v>
+      </c>
+      <c r="D152">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B153">
+        <v>167</v>
+      </c>
+      <c r="C153">
+        <v>629</v>
+      </c>
+      <c r="D153">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="2">
+        <v>46200</v>
+      </c>
+      <c r="B154">
+        <v>119</v>
+      </c>
+      <c r="C154">
+        <v>820</v>
+      </c>
+      <c r="D154">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="2">
+        <v>46201</v>
+      </c>
+      <c r="B155">
+        <v>533</v>
+      </c>
+      <c r="C155">
+        <v>652</v>
+      </c>
+      <c r="D155">
+        <v>900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
